--- a/402/402_7.xlsx
+++ b/402/402_7.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Lecture notes _2025\B.Stat 402\Practical\402 practical problem (Demography) By Anika\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C403EEC6-EC80-4E92-A98C-C0A78238CC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{72BD4945-087C-4A41-8B43-BFE56D0BAE85}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19140" windowHeight="10140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>i</t>
   </si>
@@ -121,11 +115,14 @@
   <si>
     <t>Female never married Si</t>
   </si>
+  <si>
+    <t>S bar</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -505,16 +502,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B30A93-5C71-418A-AED7-22E0D5B0C3A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" ht="63" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -530,7 +527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -544,7 +541,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -558,7 +555,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -572,7 +569,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -586,7 +583,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -600,7 +597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -614,7 +611,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -628,7 +625,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -642,7 +639,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -656,20 +653,20 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="C11">
-        <f>SUM(C2:C10)</f>
-        <v>284.10000000000002</v>
+        <f>SUM(C2:C8)</f>
+        <v>282.8</v>
       </c>
       <c r="D11">
-        <f>SUM(D2:D10)</f>
-        <v>153.99999999999997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <f>SUM(D2:D8)</f>
+        <v>153.69999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.45" x14ac:dyDescent="0.35">
       <c r="E13" t="s">
         <v>15</v>
       </c>
@@ -678,24 +675,24 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" ht="18.600000000000001" x14ac:dyDescent="0.45">
       <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="4">
         <f>(((F13+5*C11-50*((C9+C10)/2))/(100-((C9+C10)/2))))</f>
-        <v>24.036235530951185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+        <v>23.970810266733771</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18.600000000000001" x14ac:dyDescent="0.45">
       <c r="D16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="4">
         <f>((F13+5*D11-50*((D9+D10)/2))/(100-((D9+D10)/2)))</f>
-        <v>17.651477215823736</v>
+        <v>17.636454682023036</v>
       </c>
     </row>
   </sheetData>
@@ -708,14 +705,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F73826-8AAC-41D5-B37F-E5C98965671A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="10.90625" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -737,13 +735,13 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -751,13 +749,13 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -765,13 +763,13 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>72</v>
+        <v>61.5</v>
       </c>
       <c r="D4">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -779,13 +777,13 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>20.6</v>
       </c>
       <c r="D5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -793,13 +791,13 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>5.3</v>
       </c>
       <c r="D6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -807,13 +805,13 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>1.4</v>
       </c>
       <c r="D7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -821,13 +819,13 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -835,13 +833,13 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -849,26 +847,39 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11">
-        <f>SUM(C2:C10)</f>
-        <v>357.3</v>
+        <f>SUM(C2:C8)</f>
+        <v>282.8</v>
       </c>
       <c r="D11">
-        <f>SUM(D2:D10)</f>
-        <v>194.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <f>SUM(D2:D8)</f>
+        <v>153.69999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <f>0.5*(C9+C10)</f>
+        <v>0.65</v>
+      </c>
+      <c r="D12">
+        <f>0.5*(D9+D10)</f>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.45" x14ac:dyDescent="0.35">
       <c r="E13" t="s">
         <v>15</v>
       </c>
@@ -877,25 +888,26 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="14.45" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="F15">
-        <f>(((F13+5*C11-50*((C9+C10)/2))/(100-((C9+C10)/2))))</f>
-        <v>27.378640776699029</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E15">
+        <f>(F13+5*C11-50*C12)/(100-C12)</f>
+        <v>23.970810266733771</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="14.45" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>16</v>
       </c>
-      <c r="F16">
-        <f>((F13+5*D11-50*((D9+D10)/2))/(100-((D9+D10)/2)))</f>
-        <v>19.63891675025075</v>
+      <c r="E16">
+        <f>(F13+5*D11-50*D12)/(100-D12)</f>
+        <v>17.636454682023036</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>